--- a/output/関東甲信地域_赤十字病院_随意契約_X線関連_サマリー.xlsx
+++ b/output/関東甲信地域_赤十字病院_随意契約_X線関連_サマリー.xlsx
@@ -451,7 +451,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
@@ -461,7 +461,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>関東甲信地域 赤十字病院 随意契約公表情報（X線装置関連）調査サマリー</t>
+          <t>東京都・千葉県・山梨県・長野県・茨城県 赤十字病院 随意契約公表情報（X線装置関連）調査サマリー</t>
         </is>
       </c>
     </row>
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>79</v>
+        <v>155</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
       <c r="F4" s="3" t="inlineStr">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>4</v>
@@ -669,10 +669,10 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="3" t="inlineStr"/>
       <c r="F10" s="3" t="inlineStr">
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>744</v>
+        <v>831</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -861,11 +861,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -1240,26 +1240,26 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>水戸赤十字病院</t>
+          <t>日本赤十字社医療センター</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>血管造影室改修工事</t>
+          <t>据置型デジタル式X線血管造影診断装置（Artis zee BA）（シーメンス）にかかる保守契約の締結について</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>令和7年4月21日</t>
+          <t>令和7年3月7日</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1980000</v>
+        <v>19318200</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1268,47 +1268,49 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>製品</t>
+          <t>保守</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>有限会社翼建設埼玉県さいたま市北区別所町52-11 C-103</t>
+          <t>シーメンスヘルスケア株式会社東京都品川区大崎1-11-1</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://mito.jrc.or.jp/data/media/mito-jrc/uploads/2026/04/MHP_2604015/MHP_2604015.pdf</t>
+          <t>https://www.med.jrc.or.jp/Portals/0/resources/chotatsu/zuikei/zuikei_202404q.pdf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>水戸赤十字病院</t>
+          <t>日本赤十字社医療センター</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>X線一般撮影装置修理について</t>
+          <t>据置型デジタル式X線血管造影診断装置（Artis zee BA）（シーメンス）にかかる保守契約の締結について</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>令和8年2月10日</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>1650000</v>
+          <t>令和7年2月7日</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>１９，３１８，２００円</t>
+        </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>血管撮影（CVS、アンギオ）</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1318,12 +1320,12 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>島津メディカルシステムズ株式会社茨城県牛久市中央4-24-2アルシェビル102号</t>
+          <t>シーメンスヘルスケア株式会社東京都品川区大崎1-11-1</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://mito.jrc.or.jp/data/media/mito-jrc/uploads/2026/04/MHP_2604015/MHP_2604015.pdf</t>
+          <t>https://www.med.jrc.or.jp/Portals/0/resources/chotatsu/zuikei/zuikei_202404q.pdf</t>
         </is>
       </c>
     </row>
@@ -1340,16 +1342,16 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>循環器Ｘ線透視診断装置（血管撮影装置）の保守契約更新</t>
+          <t>血管造影室改修工事</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>令和6年4月3日</t>
+          <t>令和7年4月21日</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>3718000</v>
+        <v>1980000</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1358,17 +1360,17 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>保守</t>
+          <t>製品</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>シーメンスヘルスケア株式会社 千葉・茨城営業所千葉県千葉市美浜区中瀬2-6-1</t>
+          <t>有限会社翼建設埼玉県さいたま市北区別所町52-11 C-103</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://mito.jrc.or.jp/data/media/mito-jrc/uploads/2025/04/MHP_2504010/MHP_2504010.pdf</t>
+          <t>https://mito.jrc.or.jp/data/media/mito-jrc/uploads/2026/04/MHP_2604015/MHP_2604015.pdf</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1387,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>汎用Ｘ線透視診断装置（Ｘ線ＴＶ装置）の保守契約更新</t>
+          <t>X線一般撮影装置修理について</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>令和6年4月3日</t>
+          <t>令和8年2月10日</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
@@ -1398,7 +1400,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>透視撮影台（X線テレビ）</t>
+          <t>一般撮影（レントゲン）</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1408,100 +1410,235 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>シーメンスヘルスケア株式会社 千葉・茨城営業所千葉県千葉市美浜区中瀬2-6-1</t>
+          <t>島津メディカルシステムズ株式会社茨城県牛久市中央4-24-2アルシェビル102号</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://mito.jrc.or.jp/data/media/mito-jrc/uploads/2025/04/MHP_2504010/MHP_2504010.pdf</t>
+          <t>https://mito.jrc.or.jp/data/media/mito-jrc/uploads/2026/04/MHP_2604015/MHP_2604015.pdf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>長野赤十字病院</t>
+          <t>水戸赤十字病院</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>ポータブル撮影装置（島津モバイルアート1号機）の管球交換</t>
+          <t>循環器Ｘ線透視診断装置（血管撮影装置）の保守契約更新</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>令和4年10月21日</t>
+          <t>令和6年4月3日</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1888590</v>
+        <v>3718000</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>回診用X線装置</t>
+          <t>血管撮影（CVS、アンギオ）</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>製品</t>
+          <t>保守</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>丸文通称株式会社 長野県松本市鎌田一丁目11番25号</t>
+          <t>シーメンスヘルスケア株式会社 千葉・茨城営業所千葉県千葉市美浜区中瀬2-6-1</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://www.nagano-med.jrc.or.jp/wp/wp-content/uploads/R4zuikeikouhyou2.pdf</t>
+          <t>https://mito.jrc.or.jp/data/media/mito-jrc/uploads/2025/04/MHP_2504010/MHP_2504010.pdf</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>水戸赤十字病院</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>汎用Ｘ線透視診断装置（Ｘ線ＴＶ装置）の保守契約更新</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>令和6年4月3日</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>透視撮影台（X線テレビ）</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>保守</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>シーメンスヘルスケア株式会社 千葉・茨城営業所千葉県千葉市美浜区中瀬2-6-1</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>https://mito.jrc.or.jp/data/media/mito-jrc/uploads/2025/04/MHP_2504010/MHP_2504010.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>長野県</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>長野赤十字病院</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>ポータブル撮影装置（島津モバイルアート1号機）の管球交換</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>10月21日</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1888590</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>回診用X線装置</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>製品</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>丸文通称株式会社 長野県松本市鎌田一丁目11番25号</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nagano-med.jrc.or.jp/wp/wp-content/uploads/R4zuikeikouhyou2.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>長野県</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>長野赤十字病院</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>X線ｱﾝｷﾞｵｸﾞﾗﾌｨｼｽﾃﾑ（Alphenix Sky）の購入</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>3月29日</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>105600000</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>血管撮影（CVS、アンギオ）</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>製品</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>キャノンメディカルシステムズ株式会社 長野県松本市深志二丁目5番26号松本第一ビル</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nagano-med.jrc.or.jp/wp/wp-content/uploads/R4zuikeikouhyou2.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>長野県</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>飯山赤十字病院</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>一般撮影装置FPD保守点検１式</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>令和6年8月30日</t>
         </is>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E17" s="5" t="n">
         <v>20179500</v>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>一般撮影（レントゲン）</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>保守</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>丸文通商株式会社長野県松本市鎌田1丁目11番25号</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>https://www.iiyama.jrc.or.jp/file/attachment/1364.pdf</t>
         </is>

--- a/output/関東甲信地域_赤十字病院_随意契約_X線関連_サマリー.xlsx
+++ b/output/関東甲信地域_赤十字病院_随意契約_X線関連_サマリー.xlsx
@@ -451,11 +451,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>2</v>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>16</v>
@@ -865,7 +865,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>

--- a/output/関東甲信地域_赤十字病院_随意契約_X線関連_サマリー.xlsx
+++ b/output/関東甲信地域_赤十字病院_随意契約_X線関連_サマリー.xlsx
@@ -804,7 +804,7 @@
         <v>107</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr">
@@ -847,7 +847,7 @@
         <v>827</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1387,30 +1387,30 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>X線一般撮影装置修理について</t>
+          <t>Ｘ線透視撮影装置における医用画像情報システムの接続にかかる契約</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>令和8年2月10日</t>
+          <t>令和7年12月16日</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1650000</v>
+        <v>2189000</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>透視撮影台（X線テレビ）</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>保守</t>
+          <t>製品</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>島津メディカルシステムズ株式会社茨城県牛久市中央4-24-2アルシェビル102号</t>
+          <t>富士フイルムメディカル株式会社 東京支店東京都江東区有明3-5-7TOC有明イーストタワー14階</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1432,20 +1432,20 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>循環器Ｘ線透視診断装置（血管撮影装置）の保守契約更新</t>
+          <t>X線一般撮影装置修理について</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>令和6年4月3日</t>
+          <t>令和8年2月10日</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>3718000</v>
+        <v>1650000</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>血管撮影（CVS、アンギオ）</t>
+          <t>一般撮影（レントゲン）</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1455,12 +1455,12 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>シーメンスヘルスケア株式会社 千葉・茨城営業所千葉県千葉市美浜区中瀬2-6-1</t>
+          <t>島津メディカルシステムズ株式会社茨城県牛久市中央4-24-2アルシェビル102号</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://mito.jrc.or.jp/data/media/mito-jrc/uploads/2025/04/MHP_2504010/MHP_2504010.pdf</t>
+          <t>https://mito.jrc.or.jp/data/media/mito-jrc/uploads/2026/04/MHP_2604015/MHP_2604015.pdf</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>汎用Ｘ線透視診断装置（Ｘ線ＴＶ装置）の保守契約更新</t>
+          <t>循環器Ｘ線透視診断装置（血管撮影装置）の保守契約更新</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1486,11 +1486,11 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1650000</v>
+        <v>3718000</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>透視撮影台（X線テレビ）</t>
+          <t>血管撮影（CVS、アンギオ）</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1512,45 +1512,45 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>長野赤十字病院</t>
+          <t>水戸赤十字病院</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>ポータブル撮影装置（島津モバイルアート1号機）の管球交換</t>
+          <t>汎用Ｘ線透視診断装置（Ｘ線ＴＶ装置）の保守契約更新</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>10月21日</t>
+          <t>令和6年4月3日</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1888590</v>
+        <v>1650000</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>回診用X線装置</t>
+          <t>透視撮影台（X線テレビ）</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>製品</t>
+          <t>保守</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>丸文通称株式会社 長野県松本市鎌田一丁目11番25号</t>
+          <t>シーメンスヘルスケア株式会社 千葉・茨城営業所千葉県千葉市美浜区中瀬2-6-1</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://www.nagano-med.jrc.or.jp/wp/wp-content/uploads/R4zuikeikouhyou2.pdf</t>
+          <t>https://mito.jrc.or.jp/data/media/mito-jrc/uploads/2025/04/MHP_2504010/MHP_2504010.pdf</t>
         </is>
       </c>
     </row>
@@ -1567,20 +1567,20 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>X線ｱﾝｷﾞｵｸﾞﾗﾌｨｼｽﾃﾑ（Alphenix Sky）の購入</t>
+          <t>ポータブル撮影装置（島津モバイルアート1号機）の管球交換</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>3月29日</t>
+          <t>10月21日</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>105600000</v>
+        <v>1888590</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>血管撮影（CVS、アンギオ）</t>
+          <t>回診用X線装置</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>キャノンメディカルシステムズ株式会社 長野県松本市深志二丁目5番26号松本第一ビル</t>
+          <t>丸文通称株式会社 長野県松本市鎌田一丁目11番25号</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -1607,38 +1607,83 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
+          <t>長野赤十字病院</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>X線ｱﾝｷﾞｵｸﾞﾗﾌｨｼｽﾃﾑ（Alphenix Sky）の購入</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>3月29日</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>105600000</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>血管撮影（CVS、アンギオ）</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>製品</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>キャノンメディカルシステムズ株式会社 長野県松本市深志二丁目5番26号松本第一ビル</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nagano-med.jrc.or.jp/wp/wp-content/uploads/R4zuikeikouhyou2.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>長野県</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
           <t>飯山赤十字病院</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>一般撮影装置FPD保守点検１式</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>令和6年8月30日</t>
         </is>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E18" s="5" t="n">
         <v>20179500</v>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>一般撮影（レントゲン）</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>保守</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>丸文通商株式会社長野県松本市鎌田1丁目11番25号</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>https://www.iiyama.jrc.or.jp/file/attachment/1364.pdf</t>
         </is>

--- a/output/関東甲信地域_赤十字病院_随意契約_X線関連_サマリー.xlsx
+++ b/output/関東甲信地域_赤十字病院_随意契約_X線関連_サマリー.xlsx
@@ -948,7 +948,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>外科用イメージ（可搬型Cアーム透視装置）</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>血管撮影（CVS、アンギオ）</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
